--- a/Dati_Bancari.xlsx
+++ b/Dati_Bancari.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/983263f8bf5b3d54/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Programming\Corso_Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C84E1DF-9E05-4BE7-90CC-8D3964C727B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F2FD8A-B319-444A-8D78-65DF130B29AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31095" yWindow="3240" windowWidth="21600" windowHeight="12645" xr2:uid="{E6E4AD8C-5EFC-4447-9FD5-5DEF580EDD3F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{E6E4AD8C-5EFC-4447-9FD5-5DEF580EDD3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Filiali" sheetId="2" r:id="rId1"/>
@@ -7079,6 +7079,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="00000"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -7148,7 +7151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -7157,11 +7160,18 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
+    <dxf>
+      <numFmt numFmtId="165" formatCode="00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -7214,33 +7224,6 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF548235"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="25" formatCode="hh:mm"/>
     </dxf>
     <dxf>
@@ -7266,7 +7249,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FF4472C4"/>
+          <bgColor rgb="FF548235"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7304,6 +7287,30 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF4472C4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
   </dxfs>
@@ -7328,17 +7335,17 @@
     <tableColumn id="3" xr3:uid="{801A2250-F0DB-4714-9BA3-B302EB0F38EB}" name="Citta"/>
     <tableColumn id="4" xr3:uid="{68E27864-8113-40F9-9B3B-FA84B44ED94D}" name="Regione"/>
     <tableColumn id="5" xr3:uid="{0EA98265-7B7D-4BD4-AF66-06B4CC8717EE}" name="Indirizzo"/>
-    <tableColumn id="6" xr3:uid="{D2884B80-1ADE-4E39-9A22-181AAF41E8F2}" name="CAP"/>
+    <tableColumn id="6" xr3:uid="{D2884B80-1ADE-4E39-9A22-181AAF41E8F2}" name="CAP" dataDxfId="0"/>
     <tableColumn id="7" xr3:uid="{DC144EDE-2925-478C-B282-11EA50CDFAE0}" name="Telefono"/>
     <tableColumn id="8" xr3:uid="{C8FAB121-2D55-4343-81CE-CD48C3FD03F4}" name="Num_Dipendenti"/>
-    <tableColumn id="9" xr3:uid="{9215EA00-FD60-474F-BE7B-4CFE3DD96239}" name="Data_Apertura" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{9215EA00-FD60-474F-BE7B-4CFE3DD96239}" name="Data_Apertura" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C9B7A3D0-7AB1-45A6-887B-0C7FF70A128E}" name="Clienti" displayName="Clienti" ref="A1:O501" totalsRowShown="0" headerRowDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C9B7A3D0-7AB1-45A6-887B-0C7FF70A128E}" name="Clienti" displayName="Clienti" ref="A1:O501" totalsRowShown="0" headerRowDxfId="12">
   <autoFilter ref="A1:O501" xr:uid="{C9B7A3D0-7AB1-45A6-887B-0C7FF70A128E}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{7E93CAE2-13BF-463F-87E2-3DE5F3591427}" name="ID_Cliente"/>
@@ -7362,7 +7369,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{696A76CF-6729-40D3-AD42-913D0CD3D87F}" name="Conti_Correnti" displayName="Conti_Correnti" ref="A1:N101" totalsRowShown="0" headerRowDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{696A76CF-6729-40D3-AD42-913D0CD3D87F}" name="Conti_Correnti" displayName="Conti_Correnti" ref="A1:N101" totalsRowShown="0" headerRowDxfId="9">
   <autoFilter ref="A1:N101" xr:uid="{696A76CF-6729-40D3-AD42-913D0CD3D87F}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{F9F57661-FCEA-436C-9A54-C992E3C13262}" name="ID_Conto"/>
@@ -7385,7 +7392,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A6955F6-6A13-4476-A63D-E988326E203A}" name="Transazioni" displayName="Transazioni" ref="A1:J151" totalsRowShown="0" headerRowDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A6955F6-6A13-4476-A63D-E988326E203A}" name="Transazioni" displayName="Transazioni" ref="A1:J151" totalsRowShown="0" headerRowDxfId="7">
   <autoFilter ref="A1:J151" xr:uid="{6A6955F6-6A13-4476-A63D-E988326E203A}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{8B1D998F-F253-40FC-9C9F-582707F9DB5B}" name="ID_Transazione"/>
@@ -7404,7 +7411,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3D7A88C9-A30F-4B75-8A0C-9EC77201A7D6}" name="Prestiti" displayName="Prestiti" ref="A1:K51" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3D7A88C9-A30F-4B75-8A0C-9EC77201A7D6}" name="Prestiti" displayName="Prestiti" ref="A1:K51" totalsRowShown="0" headerRowDxfId="4">
   <autoFilter ref="A1:K51" xr:uid="{3D7A88C9-A30F-4B75-8A0C-9EC77201A7D6}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{213D5F21-E1BE-4907-AE20-D15AE6E947B5}" name="ID_Prestito"/>
@@ -7424,7 +7431,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{556DC5F9-B212-4FE3-91C4-BBEED69E5032}" name="Carte_Credito" displayName="Carte_Credito" ref="A1:N51" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{556DC5F9-B212-4FE3-91C4-BBEED69E5032}" name="Carte_Credito" displayName="Carte_Credito" ref="A1:N51" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A1:N51" xr:uid="{556DC5F9-B212-4FE3-91C4-BBEED69E5032}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{DD96A6C8-5BCF-4609-9399-5F5B9049A173}" name="ID_Carta"/>
@@ -7447,7 +7454,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -7764,20 +7771,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3681C0F-1713-4C45-88C2-97DAC50D3033}">
   <dimension ref="A1:I26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.59765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" style="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.73046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>2342</v>
       </c>
@@ -7793,7 +7800,7 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
       <c r="G1" t="s">
@@ -7806,7 +7813,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -7822,7 +7829,7 @@
       <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="8">
         <v>24125</v>
       </c>
       <c r="G2" t="s">
@@ -7835,7 +7842,7 @@
         <v>37669</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -7851,7 +7858,7 @@
       <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="8">
         <v>23792</v>
       </c>
       <c r="G3" t="s">
@@ -7864,7 +7871,7 @@
         <v>36770</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -7880,7 +7887,7 @@
       <c r="E4" t="s">
         <v>24</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="8">
         <v>16110</v>
       </c>
       <c r="G4" t="s">
@@ -7893,7 +7900,7 @@
         <v>38294</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -7909,7 +7916,7 @@
       <c r="E5" t="s">
         <v>30</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="8">
         <v>53978</v>
       </c>
       <c r="G5" t="s">
@@ -7922,7 +7929,7 @@
         <v>37155</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -7938,7 +7945,7 @@
       <c r="E6" t="s">
         <v>36</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="8">
         <v>33972</v>
       </c>
       <c r="G6" t="s">
@@ -7951,7 +7958,7 @@
         <v>40567</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -7967,7 +7974,7 @@
       <c r="E7" t="s">
         <v>42</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="8">
         <v>63888</v>
       </c>
       <c r="G7" t="s">
@@ -7980,7 +7987,7 @@
         <v>42583</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -7996,7 +8003,7 @@
       <c r="E8" t="s">
         <v>48</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="8">
         <v>77699</v>
       </c>
       <c r="G8" t="s">
@@ -8009,7 +8016,7 @@
         <v>42901</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -8025,7 +8032,7 @@
       <c r="E9" t="s">
         <v>54</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="8">
         <v>37109</v>
       </c>
       <c r="G9" t="s">
@@ -8038,7 +8045,7 @@
         <v>39368</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -8054,7 +8061,7 @@
       <c r="E10" t="s">
         <v>60</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="8">
         <v>23330</v>
       </c>
       <c r="G10" t="s">
@@ -8067,7 +8074,7 @@
         <v>38747</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -8083,7 +8090,7 @@
       <c r="E11" t="s">
         <v>65</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="8">
         <v>48170</v>
       </c>
       <c r="G11" t="s">
@@ -8096,7 +8103,7 @@
         <v>41543</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>67</v>
       </c>
@@ -8112,7 +8119,7 @@
       <c r="E12" t="s">
         <v>71</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="8">
         <v>16737</v>
       </c>
       <c r="G12" t="s">
@@ -8125,7 +8132,7 @@
         <v>43239</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>73</v>
       </c>
@@ -8141,7 +8148,7 @@
       <c r="E13" t="s">
         <v>76</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="8">
         <v>12779</v>
       </c>
       <c r="G13" t="s">
@@ -8154,7 +8161,7 @@
         <v>36668</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>78</v>
       </c>
@@ -8170,7 +8177,7 @@
       <c r="E14" t="s">
         <v>81</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="8">
         <v>93988</v>
       </c>
       <c r="G14" t="s">
@@ -8183,7 +8190,7 @@
         <v>43498</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>83</v>
       </c>
@@ -8199,7 +8206,7 @@
       <c r="E15" t="s">
         <v>86</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="8">
         <v>84631</v>
       </c>
       <c r="G15" t="s">
@@ -8212,7 +8219,7 @@
         <v>41181</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>88</v>
       </c>
@@ -8228,7 +8235,7 @@
       <c r="E16" t="s">
         <v>92</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="8">
         <v>73179</v>
       </c>
       <c r="G16" t="s">
@@ -8241,7 +8248,7 @@
         <v>40852</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>94</v>
       </c>
@@ -8257,7 +8264,7 @@
       <c r="E17" t="s">
         <v>97</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="8">
         <v>83633</v>
       </c>
       <c r="G17" t="s">
@@ -8270,7 +8277,7 @@
         <v>39529</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>99</v>
       </c>
@@ -8286,7 +8293,7 @@
       <c r="E18" t="s">
         <v>102</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="8">
         <v>47449</v>
       </c>
       <c r="G18" t="s">
@@ -8299,7 +8306,7 @@
         <v>37506</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>104</v>
       </c>
@@ -8315,7 +8322,7 @@
       <c r="E19" t="s">
         <v>107</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="8">
         <v>67529</v>
       </c>
       <c r="G19" t="s">
@@ -8328,7 +8335,7 @@
         <v>40174</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>109</v>
       </c>
@@ -8344,7 +8351,7 @@
       <c r="E20" t="s">
         <v>112</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="8">
         <v>96469</v>
       </c>
       <c r="G20" t="s">
@@ -8357,7 +8364,7 @@
         <v>42165</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>114</v>
       </c>
@@ -8373,7 +8380,7 @@
       <c r="E21" t="s">
         <v>118</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="8">
         <v>70478</v>
       </c>
       <c r="G21" t="s">
@@ -8386,7 +8393,7 @@
         <v>40225</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>120</v>
       </c>
@@ -8402,7 +8409,7 @@
       <c r="E22" t="s">
         <v>124</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="8">
         <v>78638</v>
       </c>
       <c r="G22" t="s">
@@ -8415,7 +8422,7 @@
         <v>38572</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>126</v>
       </c>
@@ -8431,7 +8438,7 @@
       <c r="E23" t="s">
         <v>130</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="8">
         <v>50103</v>
       </c>
       <c r="G23" t="s">
@@ -8444,7 +8451,7 @@
         <v>41741</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>132</v>
       </c>
@@ -8460,7 +8467,7 @@
       <c r="E24" t="s">
         <v>135</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="8">
         <v>38678</v>
       </c>
       <c r="G24" t="s">
@@ -8473,7 +8480,7 @@
         <v>39266</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>137</v>
       </c>
@@ -8489,7 +8496,7 @@
       <c r="E25" t="s">
         <v>140</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="8">
         <v>92888</v>
       </c>
       <c r="G25" t="s">
@@ -8502,7 +8509,7 @@
         <v>42694</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>142</v>
       </c>
@@ -8518,7 +8525,7 @@
       <c r="E26" t="s">
         <v>144</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="8">
         <v>20100</v>
       </c>
       <c r="G26" t="s">
@@ -8542,26 +8549,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D6F36C7-CF46-4EE8-BC95-533D0181EA7A}">
   <dimension ref="A1:O501"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.86328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.1328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.1328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.86328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.1328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.59765625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.86328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.73046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>146</v>
       </c>
@@ -8608,7 +8615,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>158</v>
       </c>
@@ -8655,7 +8662,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>166</v>
       </c>
@@ -8702,7 +8709,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>174</v>
       </c>
@@ -8749,7 +8756,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>180</v>
       </c>
@@ -8796,7 +8803,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>186</v>
       </c>
@@ -8843,7 +8850,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>192</v>
       </c>
@@ -8890,7 +8897,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>197</v>
       </c>
@@ -8937,7 +8944,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>202</v>
       </c>
@@ -8984,7 +8991,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>208</v>
       </c>
@@ -9031,7 +9038,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>214</v>
       </c>
@@ -9078,7 +9085,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>219</v>
       </c>
@@ -9125,7 +9132,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>224</v>
       </c>
@@ -9172,7 +9179,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>229</v>
       </c>
@@ -9219,7 +9226,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>234</v>
       </c>
@@ -9266,7 +9273,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>238</v>
       </c>
@@ -9313,7 +9320,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>242</v>
       </c>
@@ -9360,7 +9367,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>246</v>
       </c>
@@ -9407,7 +9414,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>251</v>
       </c>
@@ -9454,7 +9461,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>255</v>
       </c>
@@ -9501,7 +9508,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>260</v>
       </c>
@@ -9548,7 +9555,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>265</v>
       </c>
@@ -9595,7 +9602,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>268</v>
       </c>
@@ -9642,7 +9649,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>272</v>
       </c>
@@ -9689,7 +9696,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>276</v>
       </c>
@@ -9736,7 +9743,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>281</v>
       </c>
@@ -9783,7 +9790,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>285</v>
       </c>
@@ -9830,7 +9837,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>290</v>
       </c>
@@ -9877,7 +9884,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>296</v>
       </c>
@@ -9924,7 +9931,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>300</v>
       </c>
@@ -9971,7 +9978,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>303</v>
       </c>
@@ -10018,7 +10025,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>306</v>
       </c>
@@ -10065,7 +10072,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>310</v>
       </c>
@@ -10112,7 +10119,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>315</v>
       </c>
@@ -10159,7 +10166,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>318</v>
       </c>
@@ -10206,7 +10213,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>323</v>
       </c>
@@ -10253,7 +10260,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>328</v>
       </c>
@@ -10300,7 +10307,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>332</v>
       </c>
@@ -10347,7 +10354,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>335</v>
       </c>
@@ -10394,7 +10401,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>339</v>
       </c>
@@ -10441,7 +10448,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>343</v>
       </c>
@@ -10488,7 +10495,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>347</v>
       </c>
@@ -10535,7 +10542,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>350</v>
       </c>
@@ -10582,7 +10589,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>353</v>
       </c>
@@ -10629,7 +10636,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>357</v>
       </c>
@@ -10676,7 +10683,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>363</v>
       </c>
@@ -10723,7 +10730,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>368</v>
       </c>
@@ -10770,7 +10777,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>372</v>
       </c>
@@ -10817,7 +10824,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>375</v>
       </c>
@@ -10864,7 +10871,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>379</v>
       </c>
@@ -10911,7 +10918,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>382</v>
       </c>
@@ -10958,7 +10965,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>386</v>
       </c>
@@ -11005,7 +11012,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>389</v>
       </c>
@@ -11052,7 +11059,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>392</v>
       </c>
@@ -11099,7 +11106,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>395</v>
       </c>
@@ -11146,7 +11153,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>399</v>
       </c>
@@ -11193,7 +11200,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>404</v>
       </c>
@@ -11240,7 +11247,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>407</v>
       </c>
@@ -11287,7 +11294,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>410</v>
       </c>
@@ -11334,7 +11341,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>413</v>
       </c>
@@ -11381,7 +11388,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>416</v>
       </c>
@@ -11428,7 +11435,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>420</v>
       </c>
@@ -11475,7 +11482,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>423</v>
       </c>
@@ -11522,7 +11529,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>427</v>
       </c>
@@ -11569,7 +11576,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>430</v>
       </c>
@@ -11616,7 +11623,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>433</v>
       </c>
@@ -11663,7 +11670,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>436</v>
       </c>
@@ -11710,7 +11717,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>439</v>
       </c>
@@ -11757,7 +11764,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>442</v>
       </c>
@@ -11804,7 +11811,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>446</v>
       </c>
@@ -11851,7 +11858,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>449</v>
       </c>
@@ -11898,7 +11905,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>453</v>
       </c>
@@ -11945,7 +11952,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>456</v>
       </c>
@@ -11992,7 +11999,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>459</v>
       </c>
@@ -12039,7 +12046,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>462</v>
       </c>
@@ -12086,7 +12093,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>465</v>
       </c>
@@ -12133,7 +12140,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>468</v>
       </c>
@@ -12180,7 +12187,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>471</v>
       </c>
@@ -12227,7 +12234,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>474</v>
       </c>
@@ -12274,7 +12281,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>477</v>
       </c>
@@ -12321,7 +12328,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>480</v>
       </c>
@@ -12368,7 +12375,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>483</v>
       </c>
@@ -12415,7 +12422,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>486</v>
       </c>
@@ -12462,7 +12469,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>489</v>
       </c>
@@ -12509,7 +12516,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>492</v>
       </c>
@@ -12556,7 +12563,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>495</v>
       </c>
@@ -12603,7 +12610,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>498</v>
       </c>
@@ -12650,7 +12657,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>501</v>
       </c>
@@ -12697,7 +12704,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>504</v>
       </c>
@@ -12744,7 +12751,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>507</v>
       </c>
@@ -12791,7 +12798,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>510</v>
       </c>
@@ -12838,7 +12845,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>513</v>
       </c>
@@ -12885,7 +12892,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>516</v>
       </c>
@@ -12932,7 +12939,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>519</v>
       </c>
@@ -12979,7 +12986,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>522</v>
       </c>
@@ -13026,7 +13033,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>525</v>
       </c>
@@ -13073,7 +13080,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>528</v>
       </c>
@@ -13120,7 +13127,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>531</v>
       </c>
@@ -13167,7 +13174,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>534</v>
       </c>
@@ -13214,7 +13221,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>537</v>
       </c>
@@ -13261,7 +13268,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>540</v>
       </c>
@@ -13308,7 +13315,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>543</v>
       </c>
@@ -13355,7 +13362,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>547</v>
       </c>
@@ -13402,7 +13409,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>551</v>
       </c>
@@ -13449,7 +13456,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>554</v>
       </c>
@@ -13496,7 +13503,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>557</v>
       </c>
@@ -13543,7 +13550,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>560</v>
       </c>
@@ -13590,7 +13597,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>563</v>
       </c>
@@ -13637,7 +13644,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>566</v>
       </c>
@@ -13684,7 +13691,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>569</v>
       </c>
@@ -13731,7 +13738,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>572</v>
       </c>
@@ -13778,7 +13785,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>575</v>
       </c>
@@ -13825,7 +13832,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>578</v>
       </c>
@@ -13872,7 +13879,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>581</v>
       </c>
@@ -13919,7 +13926,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>584</v>
       </c>
@@ -13966,7 +13973,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>587</v>
       </c>
@@ -14013,7 +14020,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>590</v>
       </c>
@@ -14060,7 +14067,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>593</v>
       </c>
@@ -14107,7 +14114,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>596</v>
       </c>
@@ -14154,7 +14161,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>599</v>
       </c>
@@ -14201,7 +14208,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>602</v>
       </c>
@@ -14248,7 +14255,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>605</v>
       </c>
@@ -14295,7 +14302,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>608</v>
       </c>
@@ -14342,7 +14349,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>611</v>
       </c>
@@ -14389,7 +14396,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>614</v>
       </c>
@@ -14436,7 +14443,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>617</v>
       </c>
@@ -14483,7 +14490,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>620</v>
       </c>
@@ -14530,7 +14537,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>623</v>
       </c>
@@ -14577,7 +14584,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>626</v>
       </c>
@@ -14624,7 +14631,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>629</v>
       </c>
@@ -14671,7 +14678,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>632</v>
       </c>
@@ -14718,7 +14725,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>635</v>
       </c>
@@ -14765,7 +14772,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>638</v>
       </c>
@@ -14812,7 +14819,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>641</v>
       </c>
@@ -14859,7 +14866,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>644</v>
       </c>
@@ -14906,7 +14913,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>647</v>
       </c>
@@ -14953,7 +14960,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>651</v>
       </c>
@@ -15000,7 +15007,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>654</v>
       </c>
@@ -15047,7 +15054,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>657</v>
       </c>
@@ -15094,7 +15101,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>661</v>
       </c>
@@ -15141,7 +15148,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>664</v>
       </c>
@@ -15188,7 +15195,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>667</v>
       </c>
@@ -15235,7 +15242,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>670</v>
       </c>
@@ -15282,7 +15289,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>673</v>
       </c>
@@ -15329,7 +15336,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>676</v>
       </c>
@@ -15376,7 +15383,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>679</v>
       </c>
@@ -15423,7 +15430,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>682</v>
       </c>
@@ -15470,7 +15477,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>685</v>
       </c>
@@ -15517,7 +15524,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>688</v>
       </c>
@@ -15564,7 +15571,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>691</v>
       </c>
@@ -15611,7 +15618,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>694</v>
       </c>
@@ -15658,7 +15665,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>697</v>
       </c>
@@ -15705,7 +15712,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>700</v>
       </c>
@@ -15752,7 +15759,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>703</v>
       </c>
@@ -15799,7 +15806,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>706</v>
       </c>
@@ -15846,7 +15853,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>709</v>
       </c>
@@ -15893,7 +15900,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>712</v>
       </c>
@@ -15940,7 +15947,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>715</v>
       </c>
@@ -15987,7 +15994,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>718</v>
       </c>
@@ -16034,7 +16041,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>721</v>
       </c>
@@ -16081,7 +16088,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>724</v>
       </c>
@@ -16128,7 +16135,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>727</v>
       </c>
@@ -16175,7 +16182,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>730</v>
       </c>
@@ -16222,7 +16229,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>733</v>
       </c>
@@ -16269,7 +16276,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>736</v>
       </c>
@@ -16316,7 +16323,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>739</v>
       </c>
@@ -16363,7 +16370,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>742</v>
       </c>
@@ -16410,7 +16417,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>745</v>
       </c>
@@ -16457,7 +16464,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>748</v>
       </c>
@@ -16504,7 +16511,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>751</v>
       </c>
@@ -16551,7 +16558,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>754</v>
       </c>
@@ -16598,7 +16605,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>757</v>
       </c>
@@ -16645,7 +16652,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>760</v>
       </c>
@@ -16692,7 +16699,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>763</v>
       </c>
@@ -16739,7 +16746,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>766</v>
       </c>
@@ -16786,7 +16793,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>769</v>
       </c>
@@ -16833,7 +16840,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>772</v>
       </c>
@@ -16880,7 +16887,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>775</v>
       </c>
@@ -16927,7 +16934,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>778</v>
       </c>
@@ -16974,7 +16981,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>781</v>
       </c>
@@ -17021,7 +17028,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>784</v>
       </c>
@@ -17068,7 +17075,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>787</v>
       </c>
@@ -17115,7 +17122,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>790</v>
       </c>
@@ -17162,7 +17169,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>793</v>
       </c>
@@ -17209,7 +17216,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>796</v>
       </c>
@@ -17256,7 +17263,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>799</v>
       </c>
@@ -17303,7 +17310,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>802</v>
       </c>
@@ -17350,7 +17357,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>805</v>
       </c>
@@ -17397,7 +17404,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>808</v>
       </c>
@@ -17444,7 +17451,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>811</v>
       </c>
@@ -17491,7 +17498,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>814</v>
       </c>
@@ -17538,7 +17545,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>817</v>
       </c>
@@ -17585,7 +17592,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>820</v>
       </c>
@@ -17632,7 +17639,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>823</v>
       </c>
@@ -17679,7 +17686,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>826</v>
       </c>
@@ -17726,7 +17733,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>829</v>
       </c>
@@ -17773,7 +17780,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>832</v>
       </c>
@@ -17820,7 +17827,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>835</v>
       </c>
@@ -17867,7 +17874,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>838</v>
       </c>
@@ -17914,7 +17921,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>841</v>
       </c>
@@ -17961,7 +17968,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>844</v>
       </c>
@@ -18008,7 +18015,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>847</v>
       </c>
@@ -18055,7 +18062,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>850</v>
       </c>
@@ -18102,7 +18109,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>853</v>
       </c>
@@ -18149,7 +18156,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>856</v>
       </c>
@@ -18196,7 +18203,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>859</v>
       </c>
@@ -18243,7 +18250,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>862</v>
       </c>
@@ -18290,7 +18297,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>865</v>
       </c>
@@ -18337,7 +18344,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>868</v>
       </c>
@@ -18384,7 +18391,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>871</v>
       </c>
@@ -18431,7 +18438,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>874</v>
       </c>
@@ -18478,7 +18485,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>877</v>
       </c>
@@ -18525,7 +18532,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>880</v>
       </c>
@@ -18572,7 +18579,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>883</v>
       </c>
@@ -18619,7 +18626,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>886</v>
       </c>
@@ -18666,7 +18673,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>889</v>
       </c>
@@ -18713,7 +18720,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>892</v>
       </c>
@@ -18760,7 +18767,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>895</v>
       </c>
@@ -18807,7 +18814,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>898</v>
       </c>
@@ -18854,7 +18861,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>901</v>
       </c>
@@ -18901,7 +18908,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>904</v>
       </c>
@@ -18948,7 +18955,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>907</v>
       </c>
@@ -18995,7 +19002,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>910</v>
       </c>
@@ -19042,7 +19049,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>913</v>
       </c>
@@ -19089,7 +19096,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>916</v>
       </c>
@@ -19136,7 +19143,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>919</v>
       </c>
@@ -19183,7 +19190,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>922</v>
       </c>
@@ -19230,7 +19237,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>925</v>
       </c>
@@ -19277,7 +19284,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>928</v>
       </c>
@@ -19324,7 +19331,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>931</v>
       </c>
@@ -19371,7 +19378,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>934</v>
       </c>
@@ -19418,7 +19425,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>937</v>
       </c>
@@ -19465,7 +19472,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>940</v>
       </c>
@@ -19512,7 +19519,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>943</v>
       </c>
@@ -19559,7 +19566,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>946</v>
       </c>
@@ -19606,7 +19613,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>949</v>
       </c>
@@ -19653,7 +19660,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>952</v>
       </c>
@@ -19700,7 +19707,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>955</v>
       </c>
@@ -19747,7 +19754,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>958</v>
       </c>
@@ -19794,7 +19801,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>961</v>
       </c>
@@ -19841,7 +19848,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>964</v>
       </c>
@@ -19888,7 +19895,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>967</v>
       </c>
@@ -19935,7 +19942,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>970</v>
       </c>
@@ -19982,7 +19989,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>973</v>
       </c>
@@ -20029,7 +20036,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>976</v>
       </c>
@@ -20076,7 +20083,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>979</v>
       </c>
@@ -20123,7 +20130,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>982</v>
       </c>
@@ -20170,7 +20177,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>985</v>
       </c>
@@ -20217,7 +20224,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>988</v>
       </c>
@@ -20264,7 +20271,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>991</v>
       </c>
@@ -20311,7 +20318,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>994</v>
       </c>
@@ -20358,7 +20365,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>997</v>
       </c>
@@ -20405,7 +20412,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>1000</v>
       </c>
@@ -20452,7 +20459,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>1003</v>
       </c>
@@ -20499,7 +20506,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>1006</v>
       </c>
@@ -20546,7 +20553,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>1009</v>
       </c>
@@ -20593,7 +20600,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>1012</v>
       </c>
@@ -20640,7 +20647,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>1015</v>
       </c>
@@ -20687,7 +20694,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>1018</v>
       </c>
@@ -20734,7 +20741,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>1021</v>
       </c>
@@ -20781,7 +20788,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>1024</v>
       </c>
@@ -20828,7 +20835,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>1027</v>
       </c>
@@ -20875,7 +20882,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>1030</v>
       </c>
@@ -20922,7 +20929,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>1033</v>
       </c>
@@ -20969,7 +20976,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>1036</v>
       </c>
@@ -21016,7 +21023,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>1039</v>
       </c>
@@ -21063,7 +21070,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>1042</v>
       </c>
@@ -21110,7 +21117,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>1045</v>
       </c>
@@ -21157,7 +21164,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>1048</v>
       </c>
@@ -21204,7 +21211,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>1051</v>
       </c>
@@ -21251,7 +21258,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>1054</v>
       </c>
@@ -21298,7 +21305,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>1057</v>
       </c>
@@ -21345,7 +21352,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>1060</v>
       </c>
@@ -21392,7 +21399,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
         <v>1063</v>
       </c>
@@ -21439,7 +21446,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>1066</v>
       </c>
@@ -21486,7 +21493,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>1069</v>
       </c>
@@ -21533,7 +21540,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
         <v>1072</v>
       </c>
@@ -21580,7 +21587,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
         <v>1075</v>
       </c>
@@ -21627,7 +21634,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
         <v>1078</v>
       </c>
@@ -21674,7 +21681,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
         <v>1081</v>
       </c>
@@ -21721,7 +21728,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
         <v>1084</v>
       </c>
@@ -21768,7 +21775,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
         <v>1087</v>
       </c>
@@ -21815,7 +21822,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
         <v>1090</v>
       </c>
@@ -21862,7 +21869,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
         <v>1093</v>
       </c>
@@ -21909,7 +21916,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
         <v>1096</v>
       </c>
@@ -21956,7 +21963,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
         <v>1099</v>
       </c>
@@ -22003,7 +22010,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
         <v>1102</v>
       </c>
@@ -22050,7 +22057,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
         <v>1105</v>
       </c>
@@ -22097,7 +22104,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
         <v>1108</v>
       </c>
@@ -22144,7 +22151,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
         <v>1111</v>
       </c>
@@ -22191,7 +22198,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
         <v>1114</v>
       </c>
@@ -22238,7 +22245,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
         <v>1117</v>
       </c>
@@ -22285,7 +22292,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
         <v>1120</v>
       </c>
@@ -22332,7 +22339,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
         <v>1123</v>
       </c>
@@ -22379,7 +22386,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
         <v>1126</v>
       </c>
@@ -22426,7 +22433,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
         <v>1129</v>
       </c>
@@ -22473,7 +22480,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
         <v>1132</v>
       </c>
@@ -22520,7 +22527,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
         <v>1135</v>
       </c>
@@ -22567,7 +22574,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
         <v>1138</v>
       </c>
@@ -22614,7 +22621,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
         <v>1141</v>
       </c>
@@ -22661,7 +22668,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
         <v>1144</v>
       </c>
@@ -22708,7 +22715,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
         <v>1147</v>
       </c>
@@ -22755,7 +22762,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
         <v>1150</v>
       </c>
@@ -22802,7 +22809,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
         <v>1153</v>
       </c>
@@ -22849,7 +22856,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
         <v>1156</v>
       </c>
@@ -22896,7 +22903,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
         <v>1159</v>
       </c>
@@ -22943,7 +22950,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
         <v>1162</v>
       </c>
@@ -22990,7 +22997,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
         <v>1165</v>
       </c>
@@ -23037,7 +23044,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
         <v>1168</v>
       </c>
@@ -23084,7 +23091,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
         <v>1171</v>
       </c>
@@ -23131,7 +23138,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
         <v>1174</v>
       </c>
@@ -23178,7 +23185,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
         <v>1177</v>
       </c>
@@ -23225,7 +23232,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
         <v>1180</v>
       </c>
@@ -23272,7 +23279,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
         <v>1183</v>
       </c>
@@ -23319,7 +23326,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
         <v>1186</v>
       </c>
@@ -23366,7 +23373,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
         <v>1189</v>
       </c>
@@ -23413,7 +23420,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
         <v>1192</v>
       </c>
@@ -23460,7 +23467,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
         <v>1195</v>
       </c>
@@ -23507,7 +23514,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
         <v>1198</v>
       </c>
@@ -23554,7 +23561,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
         <v>1201</v>
       </c>
@@ -23601,7 +23608,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
         <v>1204</v>
       </c>
@@ -23648,7 +23655,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
         <v>1207</v>
       </c>
@@ -23695,7 +23702,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
         <v>1210</v>
       </c>
@@ -23742,7 +23749,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
         <v>1213</v>
       </c>
@@ -23789,7 +23796,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
         <v>1216</v>
       </c>
@@ -23836,7 +23843,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
         <v>1219</v>
       </c>
@@ -23883,7 +23890,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
         <v>1222</v>
       </c>
@@ -23930,7 +23937,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
         <v>1225</v>
       </c>
@@ -23977,7 +23984,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
         <v>1228</v>
       </c>
@@ -24024,7 +24031,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
         <v>1231</v>
       </c>
@@ -24071,7 +24078,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
         <v>1234</v>
       </c>
@@ -24118,7 +24125,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
         <v>1237</v>
       </c>
@@ -24165,7 +24172,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
         <v>1240</v>
       </c>
@@ -24212,7 +24219,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
         <v>1243</v>
       </c>
@@ -24259,7 +24266,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
         <v>1246</v>
       </c>
@@ -24306,7 +24313,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
         <v>1249</v>
       </c>
@@ -24353,7 +24360,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
         <v>1252</v>
       </c>
@@ -24400,7 +24407,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
         <v>1255</v>
       </c>
@@ -24447,7 +24454,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
         <v>1258</v>
       </c>
@@ -24494,7 +24501,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
         <v>1261</v>
       </c>
@@ -24541,7 +24548,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
         <v>1264</v>
       </c>
@@ -24588,7 +24595,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
         <v>1267</v>
       </c>
@@ -24635,7 +24642,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
         <v>1270</v>
       </c>
@@ -24682,7 +24689,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
         <v>1273</v>
       </c>
@@ -24729,7 +24736,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
         <v>1276</v>
       </c>
@@ -24776,7 +24783,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
         <v>1279</v>
       </c>
@@ -24823,7 +24830,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
         <v>1282</v>
       </c>
@@ -24870,7 +24877,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
         <v>1285</v>
       </c>
@@ -24917,7 +24924,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
         <v>1288</v>
       </c>
@@ -24964,7 +24971,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
         <v>1291</v>
       </c>
@@ -25011,7 +25018,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A351" t="s">
         <v>1294</v>
       </c>
@@ -25058,7 +25065,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
         <v>1297</v>
       </c>
@@ -25105,7 +25112,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
         <v>1300</v>
       </c>
@@ -25152,7 +25159,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
         <v>1303</v>
       </c>
@@ -25199,7 +25206,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
         <v>1306</v>
       </c>
@@ -25246,7 +25253,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
         <v>1309</v>
       </c>
@@ -25293,7 +25300,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
         <v>1312</v>
       </c>
@@ -25340,7 +25347,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
         <v>1315</v>
       </c>
@@ -25387,7 +25394,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
         <v>1318</v>
       </c>
@@ -25434,7 +25441,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
         <v>1321</v>
       </c>
@@ -25481,7 +25488,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
         <v>1324</v>
       </c>
@@ -25528,7 +25535,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A362" t="s">
         <v>1327</v>
       </c>
@@ -25575,7 +25582,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
         <v>1330</v>
       </c>
@@ -25622,7 +25629,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
         <v>1333</v>
       </c>
@@ -25669,7 +25676,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
         <v>1336</v>
       </c>
@@ -25716,7 +25723,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
         <v>1339</v>
       </c>
@@ -25763,7 +25770,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
         <v>1342</v>
       </c>
@@ -25810,7 +25817,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
         <v>1345</v>
       </c>
@@ -25857,7 +25864,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
         <v>1348</v>
       </c>
@@ -25904,7 +25911,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="370" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
         <v>1351</v>
       </c>
@@ -25951,7 +25958,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
         <v>1354</v>
       </c>
@@ -25998,7 +26005,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="372" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
         <v>1357</v>
       </c>
@@ -26045,7 +26052,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
         <v>1360</v>
       </c>
@@ -26092,7 +26099,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
         <v>1363</v>
       </c>
@@ -26139,7 +26146,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A375" t="s">
         <v>1366</v>
       </c>
@@ -26186,7 +26193,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
         <v>1369</v>
       </c>
@@ -26233,7 +26240,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
         <v>1372</v>
       </c>
@@ -26280,7 +26287,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
         <v>1375</v>
       </c>
@@ -26327,7 +26334,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
         <v>1378</v>
       </c>
@@ -26374,7 +26381,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="380" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A380" t="s">
         <v>1381</v>
       </c>
@@ -26421,7 +26428,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A381" t="s">
         <v>1384</v>
       </c>
@@ -26468,7 +26475,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="382" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A382" t="s">
         <v>1387</v>
       </c>
@@ -26515,7 +26522,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A383" t="s">
         <v>1390</v>
       </c>
@@ -26562,7 +26569,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="384" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A384" t="s">
         <v>1393</v>
       </c>
@@ -26609,7 +26616,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
         <v>1396</v>
       </c>
@@ -26656,7 +26663,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A386" t="s">
         <v>1399</v>
       </c>
@@ -26703,7 +26710,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A387" t="s">
         <v>1402</v>
       </c>
@@ -26750,7 +26757,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
         <v>1405</v>
       </c>
@@ -26797,7 +26804,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A389" t="s">
         <v>1408</v>
       </c>
@@ -26844,7 +26851,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A390" t="s">
         <v>1411</v>
       </c>
@@ -26891,7 +26898,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
         <v>1414</v>
       </c>
@@ -26938,7 +26945,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A392" t="s">
         <v>1417</v>
       </c>
@@ -26985,7 +26992,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
         <v>1420</v>
       </c>
@@ -27032,7 +27039,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
         <v>1423</v>
       </c>
@@ -27079,7 +27086,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
         <v>1426</v>
       </c>
@@ -27126,7 +27133,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A396" t="s">
         <v>1429</v>
       </c>
@@ -27173,7 +27180,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
         <v>1432</v>
       </c>
@@ -27220,7 +27227,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A398" t="s">
         <v>1435</v>
       </c>
@@ -27267,7 +27274,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A399" t="s">
         <v>1438</v>
       </c>
@@ -27314,7 +27321,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A400" t="s">
         <v>1441</v>
       </c>
@@ -27361,7 +27368,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
         <v>1444</v>
       </c>
@@ -27408,7 +27415,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A402" t="s">
         <v>1447</v>
       </c>
@@ -27455,7 +27462,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
         <v>1450</v>
       </c>
@@ -27502,7 +27509,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A404" t="s">
         <v>1453</v>
       </c>
@@ -27549,7 +27556,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A405" t="s">
         <v>1456</v>
       </c>
@@ -27596,7 +27603,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
         <v>1459</v>
       </c>
@@ -27643,7 +27650,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A407" t="s">
         <v>1462</v>
       </c>
@@ -27690,7 +27697,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A408" t="s">
         <v>1465</v>
       </c>
@@ -27737,7 +27744,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
         <v>1468</v>
       </c>
@@ -27784,7 +27791,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A410" t="s">
         <v>1471</v>
       </c>
@@ -27831,7 +27838,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A411" t="s">
         <v>1474</v>
       </c>
@@ -27878,7 +27885,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
         <v>1477</v>
       </c>
@@ -27925,7 +27932,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A413" t="s">
         <v>1480</v>
       </c>
@@ -27972,7 +27979,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A414" t="s">
         <v>1483</v>
       </c>
@@ -28019,7 +28026,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
         <v>1486</v>
       </c>
@@ -28066,7 +28073,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A416" t="s">
         <v>1489</v>
       </c>
@@ -28113,7 +28120,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
         <v>1492</v>
       </c>
@@ -28160,7 +28167,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
         <v>1495</v>
       </c>
@@ -28207,7 +28214,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
         <v>1498</v>
       </c>
@@ -28254,7 +28261,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A420" t="s">
         <v>1501</v>
       </c>
@@ -28301,7 +28308,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
         <v>1504</v>
       </c>
@@ -28348,7 +28355,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A422" t="s">
         <v>1507</v>
       </c>
@@ -28395,7 +28402,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A423" t="s">
         <v>1510</v>
       </c>
@@ -28442,7 +28449,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
         <v>1513</v>
       </c>
@@ -28489,7 +28496,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
         <v>1516</v>
       </c>
@@ -28536,7 +28543,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A426" t="s">
         <v>1519</v>
       </c>
@@ -28583,7 +28590,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A427" t="s">
         <v>1522</v>
       </c>
@@ -28630,7 +28637,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A428" t="s">
         <v>1525</v>
       </c>
@@ -28677,7 +28684,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A429" t="s">
         <v>1528</v>
       </c>
@@ -28724,7 +28731,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
         <v>1531</v>
       </c>
@@ -28771,7 +28778,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A431" t="s">
         <v>1534</v>
       </c>
@@ -28818,7 +28825,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A432" t="s">
         <v>1537</v>
       </c>
@@ -28865,7 +28872,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="433" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
         <v>1540</v>
       </c>
@@ -28912,7 +28919,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A434" t="s">
         <v>1543</v>
       </c>
@@ -28959,7 +28966,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="435" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A435" t="s">
         <v>1546</v>
       </c>
@@ -29006,7 +29013,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
         <v>1549</v>
       </c>
@@ -29053,7 +29060,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="437" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A437" t="s">
         <v>1552</v>
       </c>
@@ -29100,7 +29107,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A438" t="s">
         <v>1555</v>
       </c>
@@ -29147,7 +29154,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="439" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
         <v>1558</v>
       </c>
@@ -29194,7 +29201,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="440" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A440" t="s">
         <v>1561</v>
       </c>
@@ -29241,7 +29248,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="441" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
         <v>1564</v>
       </c>
@@ -29288,7 +29295,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="442" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
         <v>1567</v>
       </c>
@@ -29335,7 +29342,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="443" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A443" t="s">
         <v>1570</v>
       </c>
@@ -29382,7 +29389,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="444" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A444" t="s">
         <v>1573</v>
       </c>
@@ -29429,7 +29436,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="445" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
         <v>1576</v>
       </c>
@@ -29476,7 +29483,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="446" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A446" t="s">
         <v>1579</v>
       </c>
@@ -29523,7 +29530,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="447" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A447" t="s">
         <v>1582</v>
       </c>
@@ -29570,7 +29577,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="448" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
         <v>1585</v>
       </c>
@@ -29617,7 +29624,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
         <v>1588</v>
       </c>
@@ -29664,7 +29671,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
         <v>1591</v>
       </c>
@@ -29711,7 +29718,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
         <v>1594</v>
       </c>
@@ -29758,7 +29765,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
         <v>1597</v>
       </c>
@@ -29805,7 +29812,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
         <v>1600</v>
       </c>
@@ -29852,7 +29859,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
         <v>1603</v>
       </c>
@@ -29899,7 +29906,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
         <v>1606</v>
       </c>
@@ -29946,7 +29953,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
         <v>1609</v>
       </c>
@@ -29993,7 +30000,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
         <v>1612</v>
       </c>
@@ -30040,7 +30047,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
         <v>1615</v>
       </c>
@@ -30087,7 +30094,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
         <v>1618</v>
       </c>
@@ -30134,7 +30141,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
         <v>1621</v>
       </c>
@@ -30181,7 +30188,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
         <v>1624</v>
       </c>
@@ -30228,7 +30235,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
         <v>1627</v>
       </c>
@@ -30275,7 +30282,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
         <v>1630</v>
       </c>
@@ -30322,7 +30329,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
         <v>1633</v>
       </c>
@@ -30369,7 +30376,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
         <v>1636</v>
       </c>
@@ -30416,7 +30423,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A466" t="s">
         <v>1639</v>
       </c>
@@ -30463,7 +30470,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
         <v>1642</v>
       </c>
@@ -30510,7 +30517,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A468" t="s">
         <v>1645</v>
       </c>
@@ -30557,7 +30564,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
         <v>1648</v>
       </c>
@@ -30604,7 +30611,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
         <v>1651</v>
       </c>
@@ -30651,7 +30658,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A471" t="s">
         <v>1654</v>
       </c>
@@ -30698,7 +30705,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
         <v>1657</v>
       </c>
@@ -30745,7 +30752,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
         <v>1660</v>
       </c>
@@ -30792,7 +30799,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A474" t="s">
         <v>1663</v>
       </c>
@@ -30839,7 +30846,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A475" t="s">
         <v>1666</v>
       </c>
@@ -30886,7 +30893,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A476" t="s">
         <v>1669</v>
       </c>
@@ -30933,7 +30940,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A477" t="s">
         <v>1672</v>
       </c>
@@ -30980,7 +30987,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
         <v>1675</v>
       </c>
@@ -31027,7 +31034,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
         <v>1678</v>
       </c>
@@ -31074,7 +31081,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A480" t="s">
         <v>1681</v>
       </c>
@@ -31121,7 +31128,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
         <v>1684</v>
       </c>
@@ -31168,7 +31175,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A482" t="s">
         <v>1687</v>
       </c>
@@ -31215,7 +31222,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A483" t="s">
         <v>1690</v>
       </c>
@@ -31262,7 +31269,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A484" t="s">
         <v>1693</v>
       </c>
@@ -31309,7 +31316,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A485" t="s">
         <v>1696</v>
       </c>
@@ -31356,7 +31363,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
         <v>1699</v>
       </c>
@@ -31403,7 +31410,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
         <v>1702</v>
       </c>
@@ -31450,7 +31457,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
         <v>1705</v>
       </c>
@@ -31497,7 +31504,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="489" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
         <v>1708</v>
       </c>
@@ -31544,7 +31551,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
         <v>1711</v>
       </c>
@@ -31591,7 +31598,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="491" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A491" t="s">
         <v>1714</v>
       </c>
@@ -31638,7 +31645,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A492" t="s">
         <v>1717</v>
       </c>
@@ -31685,7 +31692,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A493" t="s">
         <v>1720</v>
       </c>
@@ -31732,7 +31739,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A494" t="s">
         <v>1723</v>
       </c>
@@ -31779,7 +31786,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A495" t="s">
         <v>1726</v>
       </c>
@@ -31826,7 +31833,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="496" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
         <v>1729</v>
       </c>
@@ -31873,7 +31880,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="497" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
         <v>1732</v>
       </c>
@@ -31920,7 +31927,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="498" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A498" t="s">
         <v>1735</v>
       </c>
@@ -31967,7 +31974,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="499" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
         <v>1738</v>
       </c>
@@ -32014,7 +32021,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="500" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
         <v>1741</v>
       </c>
@@ -32061,7 +32068,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="501" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A501" t="s">
         <v>1744</v>
       </c>
@@ -32119,24 +32126,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDA7CE41-1A3D-4D88-BD29-FD52FC0B7AED}">
   <dimension ref="A1:N101"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.73046875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.1328125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.86328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.59765625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>1747</v>
       </c>
@@ -32180,7 +32187,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>1759</v>
       </c>
@@ -32224,7 +32231,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1765</v>
       </c>
@@ -32268,7 +32275,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>1768</v>
       </c>
@@ -32312,7 +32319,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>1772</v>
       </c>
@@ -32356,7 +32363,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>1774</v>
       </c>
@@ -32400,7 +32407,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>1778</v>
       </c>
@@ -32444,7 +32451,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>1781</v>
       </c>
@@ -32488,7 +32495,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>1784</v>
       </c>
@@ -32532,7 +32539,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>1787</v>
       </c>
@@ -32576,7 +32583,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>1790</v>
       </c>
@@ -32620,7 +32627,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>1792</v>
       </c>
@@ -32664,7 +32671,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>1794</v>
       </c>
@@ -32708,7 +32715,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>1796</v>
       </c>
@@ -32752,7 +32759,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>1798</v>
       </c>
@@ -32796,7 +32803,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>1800</v>
       </c>
@@ -32840,7 +32847,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>1802</v>
       </c>
@@ -32884,7 +32891,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>1804</v>
       </c>
@@ -32928,7 +32935,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>1806</v>
       </c>
@@ -32972,7 +32979,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>1808</v>
       </c>
@@ -33016,7 +33023,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>1810</v>
       </c>
@@ -33060,7 +33067,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>1812</v>
       </c>
@@ -33104,7 +33111,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>1814</v>
       </c>
@@ -33148,7 +33155,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>1816</v>
       </c>
@@ -33192,7 +33199,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>1818</v>
       </c>
@@ -33236,7 +33243,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>1820</v>
       </c>
@@ -33280,7 +33287,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>1822</v>
       </c>
@@ -33324,7 +33331,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>1824</v>
       </c>
@@ -33368,7 +33375,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>1826</v>
       </c>
@@ -33412,7 +33419,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>1828</v>
       </c>
@@ -33456,7 +33463,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>1830</v>
       </c>
@@ -33500,7 +33507,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>1832</v>
       </c>
@@ -33544,7 +33551,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>1834</v>
       </c>
@@ -33588,7 +33595,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>1836</v>
       </c>
@@ -33632,7 +33639,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>1838</v>
       </c>
@@ -33676,7 +33683,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>1840</v>
       </c>
@@ -33720,7 +33727,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>1842</v>
       </c>
@@ -33764,7 +33771,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>1844</v>
       </c>
@@ -33808,7 +33815,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>1846</v>
       </c>
@@ -33852,7 +33859,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>1848</v>
       </c>
@@ -33896,7 +33903,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>1850</v>
       </c>
@@ -33940,7 +33947,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>1852</v>
       </c>
@@ -33984,7 +33991,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>1854</v>
       </c>
@@ -34028,7 +34035,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>1856</v>
       </c>
@@ -34072,7 +34079,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>1858</v>
       </c>
@@ -34116,7 +34123,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>1860</v>
       </c>
@@ -34160,7 +34167,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>1862</v>
       </c>
@@ -34204,7 +34211,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>1864</v>
       </c>
@@ -34248,7 +34255,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>1866</v>
       </c>
@@ -34292,7 +34299,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>1868</v>
       </c>
@@ -34336,7 +34343,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>1870</v>
       </c>
@@ -34380,7 +34387,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>1872</v>
       </c>
@@ -34424,7 +34431,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>1874</v>
       </c>
@@ -34468,7 +34475,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>1876</v>
       </c>
@@ -34512,7 +34519,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>1878</v>
       </c>
@@ -34556,7 +34563,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>1880</v>
       </c>
@@ -34600,7 +34607,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>1882</v>
       </c>
@@ -34644,7 +34651,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>1884</v>
       </c>
@@ -34688,7 +34695,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>1886</v>
       </c>
@@ -34732,7 +34739,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>1888</v>
       </c>
@@ -34776,7 +34783,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>1890</v>
       </c>
@@ -34820,7 +34827,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>1892</v>
       </c>
@@ -34864,7 +34871,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>1894</v>
       </c>
@@ -34908,7 +34915,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>1896</v>
       </c>
@@ -34952,7 +34959,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>1898</v>
       </c>
@@ -34996,7 +35003,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>1900</v>
       </c>
@@ -35040,7 +35047,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>1902</v>
       </c>
@@ -35084,7 +35091,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>1904</v>
       </c>
@@ -35128,7 +35135,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>1906</v>
       </c>
@@ -35172,7 +35179,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>1908</v>
       </c>
@@ -35216,7 +35223,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>1910</v>
       </c>
@@ -35260,7 +35267,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>1912</v>
       </c>
@@ -35304,7 +35311,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>1914</v>
       </c>
@@ -35348,7 +35355,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>1916</v>
       </c>
@@ -35392,7 +35399,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>1918</v>
       </c>
@@ -35436,7 +35443,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>1920</v>
       </c>
@@ -35480,7 +35487,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>1922</v>
       </c>
@@ -35524,7 +35531,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>1924</v>
       </c>
@@ -35568,7 +35575,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>1926</v>
       </c>
@@ -35612,7 +35619,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>1928</v>
       </c>
@@ -35656,7 +35663,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>1930</v>
       </c>
@@ -35700,7 +35707,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>1932</v>
       </c>
@@ -35744,7 +35751,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>1934</v>
       </c>
@@ -35788,7 +35795,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>1936</v>
       </c>
@@ -35832,7 +35839,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>1938</v>
       </c>
@@ -35876,7 +35883,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>1940</v>
       </c>
@@ -35920,7 +35927,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>1942</v>
       </c>
@@ -35964,7 +35971,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>1944</v>
       </c>
@@ -36008,7 +36015,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>1946</v>
       </c>
@@ -36052,7 +36059,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>1948</v>
       </c>
@@ -36096,7 +36103,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>1950</v>
       </c>
@@ -36140,7 +36147,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>1952</v>
       </c>
@@ -36184,7 +36191,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>1954</v>
       </c>
@@ -36228,7 +36235,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>1956</v>
       </c>
@@ -36272,7 +36279,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>1958</v>
       </c>
@@ -36316,7 +36323,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>1960</v>
       </c>
@@ -36360,7 +36367,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>1962</v>
       </c>
@@ -36404,7 +36411,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>1964</v>
       </c>
@@ -36448,7 +36455,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>1966</v>
       </c>
@@ -36492,7 +36499,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>1968</v>
       </c>
@@ -36536,7 +36543,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>1970</v>
       </c>
@@ -36591,21 +36598,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D762D15F-289F-430A-98E0-C63C2248E51D}">
   <dimension ref="A1:J151"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.265625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.1328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>1972</v>
       </c>
@@ -36637,7 +36644,7 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>1981</v>
       </c>
@@ -36669,7 +36676,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1986</v>
       </c>
@@ -36701,7 +36708,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>1990</v>
       </c>
@@ -36733,7 +36740,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>1993</v>
       </c>
@@ -36765,7 +36772,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>1995</v>
       </c>
@@ -36797,7 +36804,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>1996</v>
       </c>
@@ -36829,7 +36836,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>1998</v>
       </c>
@@ -36861,7 +36868,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>2000</v>
       </c>
@@ -36893,7 +36900,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>2002</v>
       </c>
@@ -36925,7 +36932,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>2004</v>
       </c>
@@ -36957,7 +36964,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>2006</v>
       </c>
@@ -36989,7 +36996,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>2007</v>
       </c>
@@ -37021,7 +37028,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>2008</v>
       </c>
@@ -37053,7 +37060,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>2009</v>
       </c>
@@ -37085,7 +37092,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>2011</v>
       </c>
@@ -37117,7 +37124,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>2012</v>
       </c>
@@ -37149,7 +37156,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>2013</v>
       </c>
@@ -37181,7 +37188,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>2015</v>
       </c>
@@ -37213,7 +37220,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>2016</v>
       </c>
@@ -37245,7 +37252,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>2018</v>
       </c>
@@ -37277,7 +37284,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>2019</v>
       </c>
@@ -37309,7 +37316,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>2020</v>
       </c>
@@ -37341,7 +37348,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>2021</v>
       </c>
@@ -37373,7 +37380,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>2022</v>
       </c>
@@ -37405,7 +37412,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>2023</v>
       </c>
@@ -37437,7 +37444,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>2024</v>
       </c>
@@ -37469,7 +37476,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>2025</v>
       </c>
@@ -37501,7 +37508,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>2026</v>
       </c>
@@ -37533,7 +37540,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>2027</v>
       </c>
@@ -37565,7 +37572,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>2028</v>
       </c>
@@ -37597,7 +37604,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>2029</v>
       </c>
@@ -37629,7 +37636,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>2030</v>
       </c>
@@ -37661,7 +37668,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>2031</v>
       </c>
@@ -37693,7 +37700,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>2032</v>
       </c>
@@ -37725,7 +37732,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>2033</v>
       </c>
@@ -37757,7 +37764,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>2034</v>
       </c>
@@ -37789,7 +37796,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>2035</v>
       </c>
@@ -37821,7 +37828,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>2036</v>
       </c>
@@ -37853,7 +37860,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>2037</v>
       </c>
@@ -37885,7 +37892,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>2038</v>
       </c>
@@ -37917,7 +37924,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>2039</v>
       </c>
@@ -37949,7 +37956,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>2040</v>
       </c>
@@ -37981,7 +37988,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>2041</v>
       </c>
@@ -38013,7 +38020,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>2042</v>
       </c>
@@ -38045,7 +38052,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>2044</v>
       </c>
@@ -38077,7 +38084,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>2045</v>
       </c>
@@ -38109,7 +38116,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>2046</v>
       </c>
@@ -38141,7 +38148,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>2047</v>
       </c>
@@ -38173,7 +38180,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>2048</v>
       </c>
@@ -38205,7 +38212,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>2049</v>
       </c>
@@ -38237,7 +38244,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>2050</v>
       </c>
@@ -38269,7 +38276,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>2051</v>
       </c>
@@ -38301,7 +38308,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>2052</v>
       </c>
@@ -38333,7 +38340,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>2053</v>
       </c>
@@ -38365,7 +38372,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>2054</v>
       </c>
@@ -38397,7 +38404,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>2055</v>
       </c>
@@ -38429,7 +38436,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>2056</v>
       </c>
@@ -38461,7 +38468,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>2057</v>
       </c>
@@ -38493,7 +38500,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>2058</v>
       </c>
@@ -38525,7 +38532,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>2059</v>
       </c>
@@ -38557,7 +38564,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>2060</v>
       </c>
@@ -38589,7 +38596,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>2061</v>
       </c>
@@ -38621,7 +38628,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>2062</v>
       </c>
@@ -38653,7 +38660,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>2064</v>
       </c>
@@ -38685,7 +38692,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>2065</v>
       </c>
@@ -38717,7 +38724,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>2066</v>
       </c>
@@ -38749,7 +38756,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>2067</v>
       </c>
@@ -38781,7 +38788,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>2068</v>
       </c>
@@ -38813,7 +38820,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>2069</v>
       </c>
@@ -38845,7 +38852,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>2070</v>
       </c>
@@ -38877,7 +38884,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>2071</v>
       </c>
@@ -38909,7 +38916,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>2072</v>
       </c>
@@ -38941,7 +38948,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>2073</v>
       </c>
@@ -38973,7 +38980,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>2074</v>
       </c>
@@ -39005,7 +39012,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>2075</v>
       </c>
@@ -39037,7 +39044,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>2076</v>
       </c>
@@ -39069,7 +39076,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>2077</v>
       </c>
@@ -39101,7 +39108,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>2078</v>
       </c>
@@ -39133,7 +39140,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>2079</v>
       </c>
@@ -39165,7 +39172,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>2080</v>
       </c>
@@ -39197,7 +39204,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>2081</v>
       </c>
@@ -39229,7 +39236,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>2082</v>
       </c>
@@ -39261,7 +39268,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>2083</v>
       </c>
@@ -39293,7 +39300,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>2084</v>
       </c>
@@ -39325,7 +39332,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>2085</v>
       </c>
@@ -39357,7 +39364,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>2086</v>
       </c>
@@ -39389,7 +39396,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>2087</v>
       </c>
@@ -39421,7 +39428,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>2088</v>
       </c>
@@ -39453,7 +39460,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>2089</v>
       </c>
@@ -39485,7 +39492,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>2090</v>
       </c>
@@ -39517,7 +39524,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>2091</v>
       </c>
@@ -39549,7 +39556,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>2092</v>
       </c>
@@ -39581,7 +39588,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>2093</v>
       </c>
@@ -39613,7 +39620,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>2094</v>
       </c>
@@ -39645,7 +39652,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>2095</v>
       </c>
@@ -39677,7 +39684,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>2096</v>
       </c>
@@ -39709,7 +39716,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>2097</v>
       </c>
@@ -39741,7 +39748,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>2098</v>
       </c>
@@ -39773,7 +39780,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>2099</v>
       </c>
@@ -39805,7 +39812,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>2100</v>
       </c>
@@ -39837,7 +39844,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>2101</v>
       </c>
@@ -39869,7 +39876,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>2103</v>
       </c>
@@ -39901,7 +39908,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>2104</v>
       </c>
@@ -39933,7 +39940,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>2105</v>
       </c>
@@ -39965,7 +39972,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>2106</v>
       </c>
@@ -39997,7 +40004,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>2107</v>
       </c>
@@ -40029,7 +40036,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>2108</v>
       </c>
@@ -40061,7 +40068,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>2109</v>
       </c>
@@ -40093,7 +40100,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>2110</v>
       </c>
@@ -40125,7 +40132,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>2111</v>
       </c>
@@ -40157,7 +40164,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>2112</v>
       </c>
@@ -40189,7 +40196,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>2113</v>
       </c>
@@ -40221,7 +40228,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>2114</v>
       </c>
@@ -40253,7 +40260,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>2115</v>
       </c>
@@ -40285,7 +40292,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>2116</v>
       </c>
@@ -40317,7 +40324,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>2117</v>
       </c>
@@ -40349,7 +40356,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>2118</v>
       </c>
@@ -40381,7 +40388,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>2119</v>
       </c>
@@ -40413,7 +40420,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>2120</v>
       </c>
@@ -40445,7 +40452,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>2121</v>
       </c>
@@ -40477,7 +40484,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>2122</v>
       </c>
@@ -40509,7 +40516,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>2123</v>
       </c>
@@ -40541,7 +40548,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>2124</v>
       </c>
@@ -40573,7 +40580,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>2125</v>
       </c>
@@ -40605,7 +40612,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>2126</v>
       </c>
@@ -40637,7 +40644,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>2127</v>
       </c>
@@ -40669,7 +40676,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>2128</v>
       </c>
@@ -40701,7 +40708,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>2129</v>
       </c>
@@ -40733,7 +40740,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>2130</v>
       </c>
@@ -40765,7 +40772,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>2131</v>
       </c>
@@ -40797,7 +40804,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>2132</v>
       </c>
@@ -40829,7 +40836,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>2133</v>
       </c>
@@ -40861,7 +40868,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>2134</v>
       </c>
@@ -40893,7 +40900,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>2135</v>
       </c>
@@ -40925,7 +40932,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>2136</v>
       </c>
@@ -40957,7 +40964,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>2137</v>
       </c>
@@ -40989,7 +40996,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>2138</v>
       </c>
@@ -41021,7 +41028,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>2139</v>
       </c>
@@ -41053,7 +41060,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>2140</v>
       </c>
@@ -41085,7 +41092,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>2141</v>
       </c>
@@ -41117,7 +41124,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>2142</v>
       </c>
@@ -41149,7 +41156,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>2143</v>
       </c>
@@ -41181,7 +41188,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>2144</v>
       </c>
@@ -41213,7 +41220,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>2145</v>
       </c>
@@ -41245,7 +41252,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>2146</v>
       </c>
@@ -41277,7 +41284,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>2147</v>
       </c>
@@ -41309,7 +41316,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>2148</v>
       </c>
@@ -41341,7 +41348,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>2149</v>
       </c>
@@ -41373,7 +41380,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>2150</v>
       </c>
@@ -41405,7 +41412,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>2151</v>
       </c>
@@ -41448,22 +41455,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C24A3E20-D0B4-436D-96C6-F921C024770B}">
   <dimension ref="A1:K51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>2152</v>
       </c>
@@ -41498,7 +41505,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>2160</v>
       </c>
@@ -41533,7 +41540,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>2164</v>
       </c>
@@ -41568,7 +41575,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2167</v>
       </c>
@@ -41603,7 +41610,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>2170</v>
       </c>
@@ -41638,7 +41645,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>2173</v>
       </c>
@@ -41673,7 +41680,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>2174</v>
       </c>
@@ -41708,7 +41715,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>2176</v>
       </c>
@@ -41743,7 +41750,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>2177</v>
       </c>
@@ -41778,7 +41785,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>2178</v>
       </c>
@@ -41813,7 +41820,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>2179</v>
       </c>
@@ -41848,7 +41855,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>2180</v>
       </c>
@@ -41883,7 +41890,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>2181</v>
       </c>
@@ -41918,7 +41925,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>2182</v>
       </c>
@@ -41953,7 +41960,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>2183</v>
       </c>
@@ -41988,7 +41995,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>2186</v>
       </c>
@@ -42023,7 +42030,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>2187</v>
       </c>
@@ -42058,7 +42065,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>2188</v>
       </c>
@@ -42093,7 +42100,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>2189</v>
       </c>
@@ -42128,7 +42135,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>2190</v>
       </c>
@@ -42163,7 +42170,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>2191</v>
       </c>
@@ -42198,7 +42205,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>2192</v>
       </c>
@@ -42233,7 +42240,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>2193</v>
       </c>
@@ -42268,7 +42275,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>2194</v>
       </c>
@@ -42303,7 +42310,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>2195</v>
       </c>
@@ -42338,7 +42345,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>2196</v>
       </c>
@@ -42373,7 +42380,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>2197</v>
       </c>
@@ -42408,7 +42415,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>2198</v>
       </c>
@@ -42443,7 +42450,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>2199</v>
       </c>
@@ -42478,7 +42485,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>2200</v>
       </c>
@@ -42513,7 +42520,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>2201</v>
       </c>
@@ -42548,7 +42555,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>2202</v>
       </c>
@@ -42583,7 +42590,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>2203</v>
       </c>
@@ -42618,7 +42625,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>2204</v>
       </c>
@@ -42653,7 +42660,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>2205</v>
       </c>
@@ -42688,7 +42695,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>2206</v>
       </c>
@@ -42723,7 +42730,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>2207</v>
       </c>
@@ -42758,7 +42765,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>2208</v>
       </c>
@@ -42793,7 +42800,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>2209</v>
       </c>
@@ -42828,7 +42835,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>2210</v>
       </c>
@@ -42863,7 +42870,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>2211</v>
       </c>
@@ -42898,7 +42905,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>2212</v>
       </c>
@@ -42933,7 +42940,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>2213</v>
       </c>
@@ -42968,7 +42975,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>2214</v>
       </c>
@@ -43003,7 +43010,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>2215</v>
       </c>
@@ -43038,7 +43045,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>2216</v>
       </c>
@@ -43073,7 +43080,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>2217</v>
       </c>
@@ -43108,7 +43115,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>2218</v>
       </c>
@@ -43143,7 +43150,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>2219</v>
       </c>
@@ -43178,7 +43185,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>2220</v>
       </c>
@@ -43213,7 +43220,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>2221</v>
       </c>
@@ -43259,25 +43266,25 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0FC6F5-E168-4D6D-9ED2-4D19E100736B}">
   <dimension ref="A1:N57"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.73046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.86328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.86328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.86328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.73046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.73046875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>2222</v>
       </c>
@@ -43321,7 +43328,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>2233</v>
       </c>
@@ -43365,7 +43372,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>2237</v>
       </c>
@@ -43409,7 +43416,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2240</v>
       </c>
@@ -43453,7 +43460,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>2242</v>
       </c>
@@ -43497,7 +43504,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>2244</v>
       </c>
@@ -43541,7 +43548,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>2248</v>
       </c>
@@ -43585,7 +43592,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>2251</v>
       </c>
@@ -43629,7 +43636,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>2253</v>
       </c>
@@ -43673,7 +43680,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>2255</v>
       </c>
@@ -43717,7 +43724,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>2257</v>
       </c>
@@ -43761,7 +43768,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>2260</v>
       </c>
@@ -43805,7 +43812,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>2263</v>
       </c>
@@ -43849,7 +43856,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>2265</v>
       </c>
@@ -43893,7 +43900,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>2267</v>
       </c>
@@ -43937,7 +43944,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>2269</v>
       </c>
@@ -43981,7 +43988,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>2271</v>
       </c>
@@ -44025,7 +44032,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>2273</v>
       </c>
@@ -44069,7 +44076,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>2275</v>
       </c>
@@ -44113,7 +44120,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>2277</v>
       </c>
@@ -44157,7 +44164,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>2279</v>
       </c>
@@ -44201,7 +44208,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>2281</v>
       </c>
@@ -44245,7 +44252,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>2283</v>
       </c>
@@ -44289,7 +44296,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>2285</v>
       </c>
@@ -44333,7 +44340,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>2287</v>
       </c>
@@ -44377,7 +44384,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>2289</v>
       </c>
@@ -44421,7 +44428,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>2291</v>
       </c>
@@ -44465,7 +44472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>2293</v>
       </c>
@@ -44509,7 +44516,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>2295</v>
       </c>
@@ -44553,7 +44560,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>2297</v>
       </c>
@@ -44597,7 +44604,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>2299</v>
       </c>
@@ -44641,7 +44648,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>2301</v>
       </c>
@@ -44685,7 +44692,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>2303</v>
       </c>
@@ -44729,7 +44736,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>2305</v>
       </c>
@@ -44773,7 +44780,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>2307</v>
       </c>
@@ -44817,7 +44824,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>2309</v>
       </c>
@@ -44861,7 +44868,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>2311</v>
       </c>
@@ -44905,7 +44912,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>2313</v>
       </c>
@@ -44949,7 +44956,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>2315</v>
       </c>
@@ -44993,7 +45000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>2318</v>
       </c>
@@ -45037,7 +45044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>2320</v>
       </c>
@@ -45081,7 +45088,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>2322</v>
       </c>
@@ -45125,7 +45132,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>2324</v>
       </c>
@@ -45169,7 +45176,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>2326</v>
       </c>
@@ -45213,7 +45220,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>2328</v>
       </c>
@@ -45257,7 +45264,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>2330</v>
       </c>
@@ -45301,7 +45308,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>2332</v>
       </c>
@@ -45345,7 +45352,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>2334</v>
       </c>
@@ -45389,7 +45396,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>2336</v>
       </c>
@@ -45433,7 +45440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>2338</v>
       </c>
@@ -45477,7 +45484,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>2340</v>
       </c>
@@ -45521,7 +45528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.45">
       <c r="F57" s="7"/>
     </row>
   </sheetData>
